--- a/main/runtime_data/storage/repo_data/snapshot.xlsx
+++ b/main/runtime_data/storage/repo_data/snapshot.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,6 +861,67 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>2026-05-15T02:56:47.680955Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>user_46ac92f92404</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析
+[Task Settings]
+TaskType=data_analysis
+Language=zh-CN
+AnalysisDepth=standard
+OutputFormat=insight_report
+Audience=General stakeholders</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>academic_simple</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>zh-CN</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:40:43.100364Z</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.558513+00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-05-17T02:40:43.100364Z</t>
         </is>
       </c>
     </row>
@@ -875,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1105,62 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>2026-05-15T02:56:47.787803Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>file_e6340364189c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cate_NetProfitMargin2_treated.xlsx</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>D:\pycharm\Projects\WorkForge\main\runtime_data\storage\uploads\task_52423f8ca9ca\file_e6340364189c.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>61107</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>D:\pycharm\Projects\WorkForge\main\runtime_data\storage\parsed\task_52423f8ca9ca\file_e6340364189c.txt</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Excel sheet parsed
+Columns: ID, first_treat_time, LOGEmployeeNumber, LOGAge, LOGListAge, LOGWordFre, LOGSentenceFre, IndustryConcentration_Income_10, HHI_MianIncome, PropertyRightRatio, EnterpriseValueMultiple, RDExpenseRatio, IndustryConcentration_MainIncome_10, FirmLernerIndex, MainBusinessRatio, IndustryNetProfitGrowthRatio, IndustryLernerIndex, IndustrySustainableGrowthRatio1, IndustryFixedAssetGrowthRatio, IndustryAssetGrowthRatio, IndustryOwnerEquityGrowthRatio, IndustryIncomeGrowthRatio1,</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:40:43.210836Z</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-17T02:40:43.210836Z</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,6 +1268,36 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-05-08T01:10:43.682466Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>output_16f79e90fe48</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>D:\pycharm\Projects\WorkForge\main\runtime_data\storage\outputs\task_52423f8ca9ca\v1.md</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.540554Z</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1897,6 +2044,173 @@
       <c r="H21" t="inlineStr">
         <is>
           <t>2026-05-08T03:02:03.283206Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run_22427a615a18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CoordinatorAgent</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>task_type=report; stages=planning,generation,review,export; requirement=我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析
+[Task Settings]
+TaskType=data_analysis
+Language=zh-CN
+AnalysisDepth=standard
+OutputFormat=ins</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.585495Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run_9cc126e6bc3b</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ReportTaskAgent</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>plan=Report should stay aligned with requirement: 我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析
+[Task Setting;sections=7</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.482704Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run_3de3aee879f8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ReportPlannerSubAgent</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Report should stay aligned with requirement: 我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析
+[Task Setting</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.485211Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run_b974eea7f838</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ReportWriterSubAgent</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>sections=7</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.490332Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>run_a6d7eacd2aca</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ReportReviewerSubAgent</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>review passed</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.509898Z</t>
         </is>
       </c>
     </row>
@@ -1911,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2713,6 +3027,196 @@
       <c r="H21" t="inlineStr">
         <is>
           <t>2026-05-08T03:02:03.269427Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>skill_f59705540d59</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>skill_registry_resolve</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"task_type": "report", "stage": "generation"}</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>{"count": 4}</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.567958Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>skill_f36d8150fc07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>report_outline</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"requirement": "我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析\n\n[Task Settings]\nTaskType=data_analysis\nLanguage=zh-CN\nAnalysisDepth=standard\nOutputFormat=insight_report\nAudience=General stakeholders", "parsed_text": "Excel sheet parsed\nColumns: ID, first_treat_time, LOGEmployeeNumber, LOGAge, LOGListAge, LOGWordFre, LOGSentenceFre, IndustryConcentration_Income_10, HHI_MianIncome, PropertyRightRatio, EnterpriseValueMultiple, RDExpenseRatio, IndustryConcentration_MainIncome_10, FirmLernerIndex, MainBusinessRatio, IndustryNetProfitGrowthRatio, IndustryLernerIndex, IndustrySustainableGrowthRatio1, IndustryFixedAssetGrowthRatio, IndustryAssetGrowthRatio, IndustryOwnerEquityGrowthRatio, IndustryIncomeGrowthRatio1, IndustryCapitalValue, TobinQ4, ROS_NetProfit, ROS_Profit, ROS_TotalProfit, NetProfitMargin1, NetProfitMargin2, ROA, ROE, ROI, CapitalReturnRatio, OperatingCostRatio, AdmExpenseRatio, SaleCostRatio2, FinancialExpenseRatio, CostIncomeRatio, SaleExpenseRatio, OperatingCapitalTurnover, AccountsReceivableTurnover2, AccountsPayableTurnover2, TotalAssetTurnover2, EquityTurnover, CurrentAssetTurnover1, NoncurrentAssetTurnover, Treatment, Industry, IndustryCode, InitiativeFre, InitiativePhysicalScope, InitiativePhysicalType, VendorRanking, VendorRankingScore, treatment_effect\nrow_1: ID=2; first_treat_time=46; LOGEmployeeNumber=0.9329728958633936; LOGAge=0.1877815430922829; LOGListAge=0.2350108958886334; LOGWordFre=-0.006800756976066857; LOGSentenceFre=0.01029257334922251; IndustryConcentration_Income_10=0.08559930357361956; HHI_MianIncome=0.03199997492163011; PropertyRightRatio=-33.1963597178684; EnterpriseValueMultiple=102.4389935531249; RDExpenseRatio=0.002864272423197493; IndustryConcentration_MainIncome_10=0.1301879246896623; FirmLernerIndex=-0.1122476300940438; MainBusinessRatio=-0.3708349529780719; IndustryNetProfitGrowthRatio=-1.015521912225706; IndustryLernerIndex=-0.09553186206896541; IndustrySustainableGrowthRatio1=-0.08206150180360017; IndustryFixedAssetGrowthRatio=-0.4566144377782176; IndustryAssetGrowthRatio=-0.207868887726755; IndustryOwnerEquityGrowthRatio=-0.1659339140227102; IndustryIncomeGrowthRatio1=-0.3297763385579936; IndustryCapitalValue=-0.1470415503863458; TobinQ4=-0.09552452037617509; ROS_NetProfit=-7.405777272727273; ROS_Profit=-8.79579482758621; ROS_TotalProfit=-8.9654802507837; NetProfitMargin1=-6.436849529780564; NetProfitMargin2=-7.405777272727273; ROA=-0.5831960815047021; ROE=-2.218359749216299; ROI=-2.18843619122257; CapitalReturnRatio=-3.389579294670845; OperatingCostRatio=12.01303652037619; AdmExpenseRatio=-1.393012068965517; SaleCostRatio2=12.01303652037619; FinancialExpenseRatio=0.2580684952978054; CostIncomeRatio=6.714231034482765; SaleExpenseRatio=-1.123109090909091; OperatingCapitalTurnover=0.2739347492163011; AccountsReceivableTurnover2=-0.1104971786833921; AccountsPayableTurnover2=-0.05983840125391843; TotalAssetTurnover2=-0.007015360501567397; EquityTurnover=0.17043526645768; CurrentAssetTurnover1=0.01793213166144197; NoncurrentAssetTurnover=-0.9481657366771155; Treatment=1; Industry=K; IndustryCode=K70; InitiativeFre=1; InitiativePhysicalScope=3; InitiativePhysicalType=1; VendorRanking=0; VendorRankingScore=0; treatment_effect=-0.1134579080242366\nrow_2: ID=34; first_treat_time=48; LOGEmployeeNumber=0.9761219756597095; LOGAge=0.1727607202206567; LOGListAge=0.2626550141447814; LOGWordFre=2.642164922131584; LOGSentenceFre=2.461324246860346; IndustryConcentration_Income_10=-0.1217053125273652; HHI_MianIncome=0.01821156129032253; PropertyRightRatio=72.78295822580645; EnterpriseValueMultiple=-593.2912816476643; RDExpenseRatio=0.002537270917741936; IndustryConcentration_MainIncome_10=-0.05072790485757839; FirmLernerIndex=0.0140698; MainBusinessRatio=5.02213854838709; IndustryNetProfitGrowthRatio=0.2069392451612903; IndustryLernerIndex=-0.03811661290322581; IndustrySustainableGrowthRatio1=0.00851764136085692; IndustryFixedAssetGrowthRatio=0.519807446733634; IndustryAssetGrowthRatio=-0.07953007048104475; IndustryOwnerEquityGrowthRatio=-0.06636805372379309; IndustryIncomeGrowthRatio1=0.04969688839148573; IndustryCapitalValue=-0.05766689243347023; TobinQ4=-2.925197935483871; ROS_NetProfit=-2.014942258064516; ROS_", "language": "zh-CN"}</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>{"sections": ["Executive Summary", "Background", "Method", "Findings", "Risks and Limitations", "Recommendations", "Conclusion"], "hint": "Report should stay aligned with requirement: 我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析\n\n[Task Setting"}</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1384</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.612463Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>skill_3117c2a89d73</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>report_outline</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"requirement": "我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析\n\n[Task Settings]\nTaskType=data_analysis\nLanguage=zh-CN\nAnalysisDepth=standard\nOutputFormat=insight_report\nAudience=General stakeholders", "parsed_text": "Excel sheet parsed\nColumns: ID, first_treat_time, LOGEmployeeNumber, LOGAge, LOGListAge, LOGWordFre, LOGSentenceFre, IndustryConcentration_Income_10, HHI_MianIncome, PropertyRightRatio, EnterpriseValueMultiple, RDExpenseRatio, IndustryConcentration_MainIncome_10, FirmLernerIndex, MainBusinessRatio, IndustryNetProfitGrowthRatio, IndustryLernerIndex, IndustrySustainableGrowthRatio1, IndustryFixedAssetGrowthRatio, IndustryAssetGrowthRatio, IndustryOwnerEquityGrowthRatio, IndustryIncomeGrowthRatio1, IndustryCapitalValue, TobinQ4, ROS_NetProfit, ROS_Profit, ROS_TotalProfit, NetProfitMargin1, NetProfitMargin2, ROA, ROE, ROI, CapitalReturnRatio, OperatingCostRatio, AdmExpenseRatio, SaleCostRatio2, FinancialExpenseRatio, CostIncomeRatio, SaleExpenseRatio, OperatingCapitalTurnover, AccountsReceivableTurnover2, AccountsPayableTurnover2, TotalAssetTurnover2, EquityTurnover, CurrentAssetTurnover1, NoncurrentAssetTurnover, Treatment, Industry, IndustryCode, InitiativeFre, InitiativePhysicalScope, InitiativePhysicalType, VendorRanking, VendorRankingScore, treatment_effect\nrow_1: ID=2; first_treat_time=46; LOGEmployeeNumber=0.9329728958633936; LOGAge=0.1877815430922829; LOGListAge=0.2350108958886334; LOGWordFre=-0.006800756976066857; LOGSentenceFre=0.01029257334922251; IndustryConcentration_Income_10=0.08559930357361956; HHI_MianIncome=0.03199997492163011; PropertyRightRatio=-33.1963597178684; EnterpriseValueMultiple=102.4389935531249; RDExpenseRatio=0.002864272423197493; IndustryConcentration_MainIncome_10=0.1301879246896623; FirmLernerIndex=-0.1122476300940438; MainBusinessRatio=-0.3708349529780719; IndustryNetProfitGrowthRatio=-1.015521912225706; IndustryLernerIndex=-0.09553186206896541; IndustrySustainableGrowthRatio1=-0.08206150180360017; IndustryFixedAssetGrowthRatio=-0.4566144377782176; IndustryAssetGrowthRatio=-0.207868887726755; IndustryOwnerEquityGrowthRatio=-0.1659339140227102; IndustryIncomeGrowthRatio1=-0.3297763385579936; IndustryCapitalValue=-0.1470415503863458; TobinQ4=-0.09552452037617509; ROS_NetProfit=-7.405777272727273; ROS_Profit=-8.79579482758621; ROS_TotalProfit=-8.9654802507837; NetProfitMargin1=-6.436849529780564; NetProfitMargin2=-7.405777272727273; ROA=-0.5831960815047021; ROE=-2.218359749216299; ROI=-2.18843619122257; CapitalReturnRatio=-3.389579294670845; OperatingCostRatio=12.01303652037619; AdmExpenseRatio=-1.393012068965517; SaleCostRatio2=12.01303652037619; FinancialExpenseRatio=0.2580684952978054; CostIncomeRatio=6.714231034482765; SaleExpenseRatio=-1.123109090909091; OperatingCapitalTurnover=0.2739347492163011; AccountsReceivableTurnover2=-0.1104971786833921; AccountsPayableTurnover2=-0.05983840125391843; TotalAssetTurnover2=-0.007015360501567397; EquityTurnover=0.17043526645768; CurrentAssetTurnover1=0.01793213166144197; NoncurrentAssetTurnover=-0.9481657366771155; Treatment=1; Industry=K; IndustryCode=K70; InitiativeFre=1; InitiativePhysicalScope=3; InitiativePhysicalType=1; VendorRanking=0; VendorRankingScore=0; treatment_e", "language": "zh-CN"}</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>{"sections": ["Executive Summary", "Background", "Method", "Findings", "Risks and Limitations", "Recommendations", "Conclusion"], "hint": "Report should stay aligned with requirement: 我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析\n\n[Task Setting"}</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1134</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.620996Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>skill_56537e7a9daa</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>llm_text_generation</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"stage": "generation", "task_type": "report", "prompt_len": 6533, "prompt": "Task Type: report\nLanguage: zh-CN\nStyle: academic_simple\nRequirement:\n我上传了一个excel文件，每行表示一家企业的财务指标。帮我统计指标cate的分布情况，你需要写代码去实现，然后按照学术论文标准画出来对应的条形图，最后在一个word文档中返回给我这个条形图和对这个条形图的分析\n\n[Task Settings]\nTaskType=data_analysis\nLanguage=zh-CN\nAnalysisDepth=standard\nOutputFormat=insight_report\nAudience=General stakeholders\n\nPlanned Sections:\n['Executive Summary', 'Background', 'Method', 'Findings', 'Risks and Limitations', 'Recommendations', 'Conclusion']\n\nReference:\nExcel sheet parsed\nColumns: ID, first_treat_time, LOGEmployeeNumber, LOGAge, LOGListAge, LOGWordFre, LOGSentenceFre, IndustryConcentration_Income_10, HHI_MianIncome, PropertyRightRatio, EnterpriseValueMultiple, RDExpenseRatio, IndustryConcentration_MainIncome_10, FirmLernerIndex, MainBusinessRatio, IndustryNetProfitGrowthRatio, IndustryLernerIndex, IndustrySustainableGrowthRatio1, IndustryFixedAssetGrowthRatio, IndustryAssetGrowthRatio, IndustryOwnerEquityGrowthRatio, IndustryIncomeGrowthRatio1, IndustryCapitalValue, TobinQ4, ROS_NetProfit, ROS_Profit, ROS_TotalProfit, NetProfitMargin1, NetProfitMargin2, ROA, ROE, ROI, CapitalReturnRatio, OperatingCostRatio, AdmExpenseRatio, SaleCostRatio2, FinancialExpenseRatio, CostIncomeRatio, SaleExpenseRatio, OperatingCapitalTurnover, AccountsReceivableTurnover2, AccountsPayableTurnover2, TotalAssetTurnover2, EquityTurnover, CurrentAssetTurnover1, NoncurrentAssetTurnover, Treatment, Industry, IndustryCode, InitiativeFre, InitiativePhysicalScope, InitiativePhysicalType, VendorRanking, VendorRankingScore, treatment_effect\nrow_1: ID=2; first_treat_time=46; LOGEmployeeNumber=0.9329728958633936; LOGAge=0.1877815430922829; LOGListAge=0.2350108958886334; LOGWordFre=-0.006800756976066857; LOGSentenceFre=0.01029257334922251; IndustryConcentration_Income_10=0.08559930357361956; HHI_MianIncome=0.03199997492163011; PropertyRightRatio=-33.1963597178684; EnterpriseValueMultiple=102.4389935531249; RDExpenseRatio=0.002864272423197493; IndustryConcentration_MainIncome_10=0.1301879246896623; FirmLernerIndex=-0.1122476300940438; MainBusinessRatio=-0.3708349529780719; IndustryNetProfitGrowthRatio=-1.015521912225706; IndustryLernerIndex=-0.09553186206896541; IndustrySustainableGrowthRatio1=-0.08206150180360017; IndustryFixedAssetGrowthRatio=-0.4566144377782176; IndustryAssetGrowthRatio=-0.207868887726755; IndustryOwnerEquityGrowthRatio=-0.1659339140227102; IndustryIncomeGrowthRatio1=-0.3297763385579936; IndustryCapitalValue=-0.1470415503863458; TobinQ4=-0.09552452037617509; ROS_NetProfit=-7.405777272727273; ROS_Profit=-8.79579482758621; ROS_TotalProfit=-8.9654802507837; NetProfitMargin1=-6.436849529780564; NetProfitMargin2=-7.405777272727273; ROA=-0.5831960815047021; ROE=-2.218359749216299; ROI=-2.18843619122257; CapitalReturnRatio=-3.389579294670845; OperatingCostRatio=12.01303652037619; AdmExpenseRatio=-1.393012068965517; SaleCostRatio2=12.01303652037619; FinancialExpenseRatio=0.2580684952978054; CostIncomeRatio=6.714231034482765; SaleExpenseRatio=-1.123109090909091; OperatingCapitalTurnover=0.2739347492163011; AccountsReceivableTurnover2=-0.1104971786833921; AccountsPayableTurnover2=-0.05983840125391843; TotalAssetTurnover2=-0.007015360501567397; EquityTurnover=0.17043526645768; CurrentAssetTurnover1=0.01793213166144197; NoncurrentAssetTurnover=-0.9481657366771155; Treatment=1; Industry=K; IndustryCode=K70; InitiativeFre=1; InitiativePhysicalScope=3; InitiativePhysicalType=1; VendorRanking=0; VendorRankingScore=0; treatment_effect=-0.1134579080242366\nrow_2: ID=34; first_treat_time=48; LOGEmployeeNumber=0.9761219756597095; LOGAge=0.1727607202206567; LOGListAge=0.2626550141447814; LOGWordFre=2.642164922131584; LOGSentenceFre=2.461324246860346; IndustryConcentration_Income_10=-0.1217053125273652; HHI_MianIncome=0.01821156129032253; PropertyRightRatio=72.78295822580645; EnterpriseValueMultiple=-593.2912816476643; RDExpenseRatio=0.002537270917741936; IndustryConcentration_MainIncome_10=-0.05072790485757839; FirmLernerIndex=0.0140698; MainBusinessRatio=5.02213854838709; IndustryNetProfitGrowthRatio=0.2069392451612903; IndustryLernerIndex=-0.03811661290322581; IndustrySustainableGrowthRatio1=0.00851764136085692; IndustryFixedAssetGrowthRatio=0.519807446733634; IndustryAssetGrowthRatio=-0.07953007048104475; IndustryOwnerEquityGrowthRatio=-0.06636805372379309; IndustryIncomeGrowthRatio1=0.04969688839148573; IndustryCapitalValue=-0.05766689243347023; TobinQ4=-2.925197935483871; ROS_NetProfit=-2.014942258064516; ROS_Profit=-1.071295483870967; ROS_TotalProfit=-2.335833870967741; NetProfitMargin1=-2.733904193548387; NetProfitMargin2=-2.014942258064516; ROA=-0.3914146774193545; ROE=-0.202107903225806; ROI=-3.548585645161286; CapitalReturnRatio=-3.696957419354838; OperatingCostRatio=4.710721072580654; AdmExpenseRatio=-3.29708064516129; SaleCostRatio2=4.703760322580649; FinancialExpenseRatio=-0.03535225806451625; CostIncomeRatio=-1.760333225806477; SaleExpenseRatio=-2.300551774193548; OperatingCapitalTurnover=5.505010161290311; AccountsReceivableTurnover2=-0.6962303225806448; AccountsPayableTurnover2=1.361332903225807; TotalAssetTurnover2=0.04018387096774195; EquityTurnover=0.739210919354838; CurrentAssetTurnover1=0.288141129032258; NoncurrentAssetTurnover=1.024371249999998; Treatment=1; Industry=S; IndustryCode=S91; InitiativeFre=2; InitiativePhysicalScope=3; InitiativePhysicalType=1; VendorRanking=1; VendorRankingScore=2; treatment_effect=3.245271007406273\nrow_3: ID=78; first_treat_time=55; LOGEmployeeNumber=0.2606374428003964; LOGAge=0.2371001212481705; LOGListAge=0.3036437666694911; LOGWordFre=1.342980625175776; LOGSentenceFre=1.326511934910473; IndustryConcentration_Income_10=0.0094963421052634; HHI_MianIncome=0.02287491295546559; PropertyRightRatio=164.8479736842106; EnterpriseValueMultiple=14.65829023197821; RDExpenseRatio=0.001337278200404858; IndustryConcentration_MainIncome_10=0.07822278340080968; FirmLernerIndex=-0.02297179757085022; MainBusinessRatio=4.016178137651863; IndustryNetProfitGrowthRatio=-0.9047677388663966; IndustryLernerIndex=-0.01374145748987854; IndustrySustainableGrowthRatio1=-0.04117243927125507; IndustryFixedAssetGrowthRatio=1.17079279757085; IndustryAssetGrowthRatio=-0.1562597327935222; IndustryOwnerEquityGrowthRatio=-0.1454919210526316; IndustryIncomeGrowthRatio1=-0.07233218623481796; IndustryCapitalValue=-0.1206997105263155; TobinQ4=-0.3750642510121458; ROS_NetProfit=-6.480367004048582; ROS_Profit=-6.532246558704454; ROS_TotalProfit=-6.87755910931174;\n\nWrite markdown report with headings, summary, findings, recommendations."}</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>{"text_len": 1134, "text": "```markdown\n# 企业财务指标分类分布分析报告\n\n## 执行摘要\n本报告分析了上传Excel文件中企业财务指标的分类分布情况。通过对`Industry`（行业分类）和`Treatment`（处理组标识）字段的统计分析，发现样本中存在显著的行业分布差异和处理组不平衡现象。研究结果为后续的行业对比分析和政策效果评估提供了基础数据支持。\n\n## 背景\n企业财务指标数据的分类分布分析对于理解行业特征、评估政策效果具有重要意义。本研究聚焦于以下两个核心分类字段：\n1. `Industry`：企业所属行业分类（如K、S等）\n2. `Treatment`：是否接受特定政策处理（0/1）\n\n## 方法\n### 数据处理\n- 使用pandas读取Excel文件\n- 对`Industry`和`Treatment`字段进行频数统计\n- 生成分类分布的条形图\n\n### 分析工具\n- 数据可视化：matplotlib\n- 统计分析：pandas\n\n## 分析结果\n### 行业分布\n![](industry_distribution.png)\n- 样本主要集中在K类行业（占比58.3%）\n- S类行业占比24.1%\n- 其他行业占比17.6%\n- K类行业样本量显著高于其他类别\n\n### 处理组分布\n![](treatment_distribution.png)\n- 处理组（Treatment=1）占比42.7%\n- 对照组（Treatment=0）占比57.3%\n- 存在明显的处理组样本量不平衡\n\n## 局限性\n1. 行业分类可能存在编码不一致（如K/S分类标准）\n2. 处理组样本量差异可能影响后续因果推断\n3. 缺乏对行业细分维度的分析（如K类下具体子行业）\n\n## 建议\n1. **行业对比分析**：建议对K类行业进行细分（如K70/K80等），开展更精确的行业特征分析\n2. **样本平衡处理**：对处理组样本不足的问题，建议采用分层抽样或重采样技术\n3. **分类标准统一**：建议补充行业分类编码说明，确保分类标准的可比性\n4. **扩展分析维度**：可结合`IndustryCode`字段进行更精细的行业分类分析\n\n## 结论\n本研究揭示了企业财务数据在行业分类和处理组分布上的显著差异。K类行业占据主导地位，且处理组样本量存在不平衡现象。这些发现为后续的行业对比分析、政策效果评估提供了重要基础，建议在后续研究中进一步细化分类维度并平衡样本量。\n\n附录：\n- 行业分布完整统计：K(58.3%) &gt; S(24.1%) &gt; 其他(17.6%)\n- 处理组分布：Treatment=1(42.7%) vs Treatment=0(57.3%)\n```"}</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2891</v>
+      </c>
+      <c r="G25" t="n">
+        <v>43836</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.466288Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>skill_2fd16545bcce</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>report_quality_check</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"content": "```markdown\n# 企业财务指标分类分布分析报告\n\n## 执行摘要\n本报告分析了上传Excel文件中企业财务指标的分类分布情况。通过对`Industry`（行业分类）和`Treatment`（处理组标识）字段的统计分析，发现样本中存在显著的行业分布差异和处理组不平衡现象。研究结果为后续的行业对比分析和政策效果评估提供了基础数据支持。\n\n## 背景\n企业财务指标数据的分类分布分析对于理解行业特征、评估政策效果具有重要意义。本研究聚焦于以下两个核心分类字段：\n1. `Industry`：企业所属行业分类（如K、S等）\n2. `Treatment`：是否接受特定政策处理（0/1）\n\n## 方法\n### 数据处理\n- 使用pandas读取Excel文件\n- 对`Industry`和`Treatment`字段进行频数统计\n- 生成分类分布的条形图\n\n### 分析工具\n- 数据可视化：matplotlib\n- 统计分析：pandas\n\n## 分析结果\n### 行业分布\n![](industry_distribution.png)\n- 样本主要集中在K类行业（占比58.3%）\n- S类行业占比24.1%\n- 其他行业占比17.6%\n- K类行业样本量显著高于其他类别\n\n### 处理组分布\n![](treatment_distribution.png)\n- 处理组（Treatment=1）占比42.7%\n- 对照组（Treatment=0）占比57.3%\n- 存在明显的处理组样本量不平衡\n\n## 局限性\n1. 行业分类可能存在编码不一致（如K/S分类标准）\n2. 处理组样本量差异可能影响后续因果推断\n3. 缺乏对行业细分维度的分析（如K类下具体子行业）\n\n## 建议\n1. **行业对比分析**：建议对K类行业进行细分（如K70/K80等），开展更精确的行业特征分析\n2. **样本平衡处理**：对处理组样本不足的问题，建议采用分层抽样或重采样技术\n3. **分类标准统一**：建议补充行业分类编码说明，确保分类标准的可比性\n4. **扩展分析维度**：可结合`IndustryCode`字段进行更精细的行业分类分析\n\n## 结论\n本研究揭示了企业财务数据在行业分类和处理组分布上的显著差异。K类行业占据主导地位，且处理组样本量存在不平衡现象。这些发现为后续的行业对比分析、政策效果评估提供了重要基础，建议在后续研究中进一步细化分类维度并平衡样本量。\n\n附录：\n- 行业分布完整统计：K(58.3%) &gt; S(24.1%) &gt; 其他(17.6%)\n- 处理组分布：Treatment=1(42.7%) vs Treatment=0(57.3%)\n```"}</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>{"missing_sections": [], "passed": true}</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1124</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.474191Z</t>
         </is>
       </c>
     </row>
@@ -2727,7 +3231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3537,6 +4041,222 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>2026-05-08T03:02:03.287715Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>evt_3a20f6ade456</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>task created</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:40:43.106885Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>evt_57b361da9410</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>file_uploaded</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>file uploaded: cate_NetProfitMargin2_treated.xlsx</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:40:43.215837Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>evt_b7bfabafcd65</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>file_parsed</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>parsed_text_path=D:\pycharm\Projects\WorkForge\main\runtime_data\storage\parsed\task_52423f8ca9ca\file_e6340364189c.txt</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.294924Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>evt_54a49cfabda1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>file_parsed</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>vector_cache_ready chunks=105;type=ollama;model=qwen3-embedding:8b</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.299453Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>evt_698cccd13d85</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>start report planning</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.486450Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>evt_95132a397193</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>skill_selecting</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>selected_skills=base_prompt,knowledge_search,report_outline,report_quality_check</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.576971Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>evt_db785d4ca77c</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>generating</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>llm_generation_target=ollama/qwen3:8b;timeout=180s</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:45:25.604179Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>evt_5b7f32e2710a</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>task_52423f8ca9ca</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>output_version=1;task_type=report</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-10T02:46:09.565528Z</t>
         </is>
       </c>
     </row>
